--- a/output/stock_quant_scores/ASML_info.xlsx
+++ b/output/stock_quant_scores/ASML_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FP2"/>
+  <dimension ref="A1:FT2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1051,235 +1051,255 @@
       </c>
       <c r="DV1" s="1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>dividendDate</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="FQ1" s="1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="FR1" s="1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DX1" s="1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DY1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DZ1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EA1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>dividendDate</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1359,7 +1379,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Christophe D. Fouquet', 'age': 51, 'title': 'President, CEO and Chair of the Board of Management', 'yearBorn': 1973, 'fiscalYear': 2024, 'totalPay': 3168381, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Roger J. M. Dassen Ph.D.', 'age': 59, 'title': 'Executive VP, CFO &amp; Member of the Management Board', 'yearBorn': 1965, 'fiscalYear': 2024, 'totalPay': 2328199, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Frederic J. M. Schneider-Maunoury', 'age': 63, 'title': 'Executive VP, COO &amp; Member of the Management Board', 'yearBorn': 1961, 'fiscalYear': 2024, 'totalPay': 2350620, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. James P. Koonmen', 'age': 57, 'title': 'Executive VP, Chief Customer Officer &amp; Member of Management Board', 'yearBorn': 1967, 'fiscalYear': 2024, 'totalPay': 1968677, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wayne R. Allan', 'age': 57, 'title': 'Executive VP, Chief Strategic Sourcing &amp; Procurement Officer and Member of Management Board', 'yearBorn': 1967, 'fiscalYear': 2024, 'totalPay': 2449742, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Jim  Kavanagh', 'title': 'Vice President of Investor Relations', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ron  Kool', 'title': 'Head of Business Performance Improvement', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Rob Van Vliet', 'title': 'Investor Relations Manager', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Peter  Convertito', 'title': 'Director Investor Relations- North America', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Christophe D. Fouquet', 'age': 51, 'title': 'President, CEO and Chair of the Board of Management', 'yearBorn': 1973, 'fiscalYear': 2024, 'totalPay': 3140618, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Roger J. M. Dassen Ph.D.', 'age': 59, 'title': 'Executive VP, CFO &amp; Member of the Management Board', 'yearBorn': 1965, 'fiscalYear': 2024, 'totalPay': 2307798, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Frederic J. M. Schneider-Maunoury', 'age': 63, 'title': 'Executive VP, COO &amp; Member of the Management Board', 'yearBorn': 1961, 'fiscalYear': 2024, 'totalPay': 2330022, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. James P. Koonmen', 'age': 57, 'title': 'Executive VP, Chief Customer Officer &amp; Member of Management Board', 'yearBorn': 1967, 'fiscalYear': 2024, 'totalPay': 1951427, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wayne R. Allan', 'age': 57, 'title': 'Executive VP, Chief Strategic Sourcing &amp; Procurement Officer and Member of Management Board', 'yearBorn': 1967, 'fiscalYear': 2024, 'totalPay': 2428276, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Jim  Kavanagh', 'title': 'Vice President of Investor Relations', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ron  Kool', 'title': 'Head of Business Performance Improvement', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Rob Van Vliet', 'title': 'Investor Relations Manager', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Peter  Convertito', 'title': 'Director Investor Relations- North America', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -1382,34 +1402,34 @@
         <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>963.51</v>
+        <v>949.55</v>
       </c>
       <c r="W2" t="n">
-        <v>949.6</v>
+        <v>946.235</v>
       </c>
       <c r="X2" t="n">
-        <v>940.95</v>
+        <v>942.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>953.6</v>
+        <v>955.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>963.51</v>
+        <v>949.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>949.6</v>
+        <v>946.235</v>
       </c>
       <c r="AB2" t="n">
-        <v>940.95</v>
+        <v>942.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>953.6</v>
+        <v>955.22</v>
       </c>
       <c r="AD2" t="n">
         <v>7.39</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="AF2" t="n">
         <v>1753747200</v>
@@ -1424,40 +1444,40 @@
         <v>1.249</v>
       </c>
       <c r="AJ2" t="n">
-        <v>33.5813</v>
+        <v>33.670204</v>
       </c>
       <c r="AK2" t="n">
-        <v>35.505615</v>
+        <v>35.63745</v>
       </c>
       <c r="AL2" t="n">
-        <v>1101935</v>
+        <v>952592</v>
       </c>
       <c r="AM2" t="n">
-        <v>1101935</v>
+        <v>952592</v>
       </c>
       <c r="AN2" t="n">
-        <v>1810026</v>
+        <v>1799263</v>
       </c>
       <c r="AO2" t="n">
-        <v>1917460</v>
+        <v>1885160</v>
       </c>
       <c r="AP2" t="n">
-        <v>1917460</v>
+        <v>1885160</v>
       </c>
       <c r="AQ2" t="n">
-        <v>683.64</v>
+        <v>950.28</v>
       </c>
       <c r="AR2" t="n">
-        <v>949.58</v>
+        <v>952.24</v>
       </c>
       <c r="AS2" t="n">
         <v>2</v>
       </c>
       <c r="AT2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="n">
-        <v>372753825792</v>
+        <v>374808444928</v>
       </c>
       <c r="AV2" t="n">
         <v>578.51</v>
@@ -1472,19 +1492,19 @@
         <v>2.374188</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11.589415</v>
+        <v>11.6532955</v>
       </c>
       <c r="BA2" t="n">
-        <v>767.111</v>
+        <v>777.6236</v>
       </c>
       <c r="BB2" t="n">
-        <v>736.11957</v>
+        <v>739.6576</v>
       </c>
       <c r="BC2" t="n">
         <v>3.36</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.0034872496</v>
+        <v>0.0035385182</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1495,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>369713774592</v>
+        <v>365068845056</v>
       </c>
       <c r="BH2" t="n">
         <v>0.29273</v>
@@ -1507,40 +1527,40 @@
         <v>393200230</v>
       </c>
       <c r="BK2" t="n">
-        <v>2694717</v>
+        <v>2239653</v>
       </c>
       <c r="BL2" t="n">
-        <v>2530748</v>
+        <v>2896648</v>
       </c>
       <c r="BM2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BN2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.0069</v>
+        <v>0.0057</v>
       </c>
       <c r="BP2" t="n">
         <v>0.00014</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.17785999</v>
+        <v>0.17787</v>
       </c>
       <c r="BR2" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.0076</v>
+        <v>0.0064</v>
       </c>
       <c r="BT2" t="n">
-        <v>396057105</v>
+        <v>393904947</v>
       </c>
       <c r="BU2" t="n">
         <v>45.478</v>
       </c>
       <c r="BV2" t="n">
-        <v>20.845243</v>
+        <v>20.922644</v>
       </c>
       <c r="BW2" t="n">
         <v>1735603200</v>
@@ -1558,7 +1578,7 @@
         <v>9415199744</v>
       </c>
       <c r="CB2" t="n">
-        <v>28.23</v>
+        <v>28.26</v>
       </c>
       <c r="CC2" t="n">
         <v>26.7</v>
@@ -1572,16 +1592,16 @@
         <v>1191196800</v>
       </c>
       <c r="CF2" t="n">
-        <v>11.495</v>
+        <v>11.35</v>
       </c>
       <c r="CG2" t="n">
-        <v>30.576</v>
+        <v>30.192</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.1776259</v>
+        <v>0.14193821</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.847</v>
@@ -1595,19 +1615,19 @@
         </is>
       </c>
       <c r="CM2" t="n">
-        <v>948</v>
+        <v>951.52</v>
       </c>
       <c r="CN2" t="n">
-        <v>1071.8394</v>
+        <v>1069.0785</v>
       </c>
       <c r="CO2" t="n">
-        <v>600.28174</v>
+        <v>598.73553</v>
       </c>
       <c r="CP2" t="n">
-        <v>857.3071</v>
+        <v>855.0988</v>
       </c>
       <c r="CQ2" t="n">
-        <v>859.1319</v>
+        <v>856.91895</v>
       </c>
       <c r="CR2" t="n">
         <v>1.78947</v>
@@ -1715,174 +1735,186 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
+      <c r="DV2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>795277800000</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.10930291</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>950.48</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-1.0400391</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>1.97003</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>942.75 - 955.22</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>NasdaqGS</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>1799263</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>373.01</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>0.6447771</v>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>578.51 - 977.48</t>
+        </is>
+      </c>
+      <c r="EH2" t="n">
+        <v>-25.95996</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>-0.026558049</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>14.193821</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>1754438400</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>1760531400</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>1760531400</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>1760531400</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>1752670800</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>1752670800</v>
+      </c>
+      <c r="EQ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>23.91594</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>39.78602</v>
+      </c>
+      <c r="EV2" t="inlineStr">
         <is>
           <t>ASML Holding N.V. - New York Re</t>
         </is>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="EW2" t="inlineStr">
         <is>
           <t>ASML Holding N.V.</t>
         </is>
       </c>
-      <c r="DY2" t="b">
-        <v>1</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>795277800000</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-15.51001</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>940.95 - 953.6</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>NasdaqGS</t>
-        </is>
-      </c>
-      <c r="ED2" t="n">
-        <v>1810026</v>
-      </c>
-      <c r="EE2" t="inlineStr">
+      <c r="EX2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EY2" t="n">
+        <v>1758931143</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>1758916800</v>
+      </c>
+      <c r="FA2" t="inlineStr">
         <is>
           <t>NMS</t>
         </is>
       </c>
-      <c r="EF2" t="inlineStr">
+      <c r="FB2" t="inlineStr">
         <is>
           <t>finmb_388904</t>
         </is>
       </c>
-      <c r="EG2" t="inlineStr">
+      <c r="FC2" t="inlineStr">
         <is>
           <t>America/New_York</t>
         </is>
       </c>
-      <c r="EH2" t="inlineStr">
+      <c r="FD2" t="inlineStr">
         <is>
           <t>EDT</t>
         </is>
       </c>
-      <c r="EI2" t="n">
+      <c r="FE2" t="n">
         <v>-14400000</v>
       </c>
-      <c r="EJ2" t="inlineStr">
+      <c r="FF2" t="inlineStr">
         <is>
           <t>us_market</t>
         </is>
       </c>
-      <c r="EK2" t="b">
+      <c r="FG2" t="b">
         <v>0</v>
       </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EM2" t="n">
-        <v>1758740015</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>-1.6097404</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>948</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>369.49</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>0.6386925</v>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>578.51 - 977.48</t>
-        </is>
-      </c>
-      <c r="ES2" t="n">
-        <v>-29.47998</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>-0.030159166</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>17.762589</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>1754438400</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>1760531400</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>1760531400</v>
-      </c>
-      <c r="EY2" t="n">
-        <v>1760531400</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>1752670800</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>1752670800</v>
-      </c>
-      <c r="FB2" t="b">
+      <c r="FH2" t="n">
+        <v>0.20747</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>951.52</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>173.89642</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>0.22362545</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>211.86243</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>0.2864331</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FO2" t="n">
         <v>0</v>
       </c>
-      <c r="FC2" t="n">
-        <v>28.23</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>23.91594</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>39.638836</v>
-      </c>
-      <c r="FG2" t="n">
-        <v>180.88898</v>
-      </c>
-      <c r="FH2" t="n">
-        <v>0.23580547</v>
-      </c>
-      <c r="FI2" t="n">
-        <v>211.88043</v>
-      </c>
-      <c r="FJ2" t="n">
-        <v>0.28783426</v>
-      </c>
-      <c r="FK2" t="n">
-        <v>15</v>
-      </c>
-      <c r="FL2" t="n">
+      <c r="FP2" t="inlineStr">
+        <is>
+          <t>1.8 - Buy</t>
+        </is>
+      </c>
+      <c r="FQ2" t="b">
         <v>0</v>
       </c>
-      <c r="FM2" t="inlineStr">
-        <is>
-          <t>1.8 - Buy</t>
-        </is>
-      </c>
-      <c r="FN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FO2" t="inlineStr">
+      <c r="FR2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="FS2" t="inlineStr">
         <is>
           <t>ASML Holding</t>
         </is>
       </c>
-      <c r="FP2" t="n">
-        <v>1.796</v>
+      <c r="FT2" t="n">
+        <v>1.7725</v>
       </c>
     </row>
   </sheetData>
